--- a/resultados/terraroxa/inventario_externos.xlsx
+++ b/resultados/terraroxa/inventario_externos.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G87"/>
+  <dimension ref="A1:G98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3403,6 +3403,391 @@
         </is>
       </c>
     </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>terraroxa</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>https://nfse-terraroxa.atende.net/autoatendimento/servicos/acesso-ao-sistema-fiscal/detalhar/1</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>nfse-terraroxa.atende.net</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>Acessar</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>https://terraroxa.atende.net/autoatendimento/servicos/acesso-ao-sistema-fiscal?perfil=false_false</t>
+        </is>
+      </c>
+      <c r="F88" t="n">
+        <v>3</v>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>2026-08-10 14:50:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>terraroxa</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>http://www.comprasgovernamentais.gov.br</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>www.comprasgovernamentais.gov.br</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>www.comprasgovernamentais.gov.br</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>https://www.terraroxa.pr.gov.br/autoatendimento/servicos/e-pregao-eletronico-cadastro-sicaf?perfil=5_1</t>
+        </is>
+      </c>
+      <c r="F89" t="n">
+        <v>3</v>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>2026-08-10 15:03:35</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>terraroxa</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>https://www.comprasgovernamentais.gov.br/index.php/sicaf</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>www.comprasgovernamentais.gov.br</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>SICAF</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>https://www.terraroxa.pr.gov.br/autoatendimento/servicos/e-pregao-eletronico-cadastro-sicaf?perfil=5_1</t>
+        </is>
+      </c>
+      <c r="F90" t="n">
+        <v>3</v>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>2026-08-10 15:03:35</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>terraroxa</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>https://sso.acesso.gov.br/login?client_id=acesso.gov.br</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>sso.acesso.gov.br</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>Portal Gov.br</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>https://www.terraroxa.pr.gov.br/autoatendimento/servicos/e-pregao-eletronico-cadastro-sicaf?perfil=5_1</t>
+        </is>
+      </c>
+      <c r="F91" t="n">
+        <v>3</v>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>2026-08-10 15:03:35</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>terraroxa</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>https://www3.comprasnet.gov.br/sicaf-web/index.jsf</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>www3.comprasnet.gov.br</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>(SICAF</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>https://www.terraroxa.pr.gov.br/autoatendimento/servicos/e-pregao-eletronico-cadastro-sicaf?perfil=5_1</t>
+        </is>
+      </c>
+      <c r="F92" t="n">
+        <v>3</v>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>2026-08-10 15:03:35</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>terraroxa</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>http://portaldeservicos.planejamento.gov.br/</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>portaldeservicos.planejamento.gov.br</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>http://portaldeservicos.planejamento.gov.br</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>https://www.terraroxa.pr.gov.br/autoatendimento/servicos/e-pregao-eletronico-cadastro-sicaf?perfil=5_1</t>
+        </is>
+      </c>
+      <c r="F93" t="n">
+        <v>3</v>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>2026-08-10 15:03:35</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>terraroxa</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=t_-3DLBLq4Q&amp;feature=youtu.be</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>www.youtube.com</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>Promocional</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>https://www.terraroxa.pr.gov.br/autoatendimento/servicos/e-pregao-eletronico-cadastro-sicaf?perfil=5_1</t>
+        </is>
+      </c>
+      <c r="F94" t="n">
+        <v>3</v>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>2026-08-10 15:03:35</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>terraroxa</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=Ke3ctbwqhtE</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>www.youtube.com</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>Novas Regras</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>https://www.terraroxa.pr.gov.br/autoatendimento/servicos/e-pregao-eletronico-cadastro-sicaf?perfil=5_1</t>
+        </is>
+      </c>
+      <c r="F95" t="n">
+        <v>3</v>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>2026-08-10 15:03:35</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>terraroxa</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>https://www.comprasgovernamentais.gov.br/index.php/sicaf-100digital-faq</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>www.comprasgovernamentais.gov.br</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>Perguntas e Respostas – SICAF 100% Digital</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>https://www.terraroxa.pr.gov.br/autoatendimento/servicos/e-pregao-eletronico-cadastro-sicaf?perfil=5_1</t>
+        </is>
+      </c>
+      <c r="F96" t="n">
+        <v>3</v>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>2026-08-10 15:03:35</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>terraroxa</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>https://www.comprasnet.gov.br/acesso.asp?url=/cadastro/cadastronovo.asp</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>www.comprasnet.gov.br</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>clicando aqui</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>https://www.terraroxa.pr.gov.br/autoatendimento/servicos/e-pregao-eletronico-cadastro-sicaf?perfil=5_1</t>
+        </is>
+      </c>
+      <c r="F97" t="n">
+        <v>3</v>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>2026-08-10 15:03:35</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>terraroxa</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>https://demonstra.serpro.gov.br/tutoriais/comprasnet_pregao_eletronico_20191202-16-28-20/html/index.html?mod=1</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>demonstra.serpro.gov.br</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>Acessar</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>https://www.terraroxa.pr.gov.br/autoatendimento/servicos/e-pregao-eletronico-comprasnet?perfil=5_1</t>
+        </is>
+      </c>
+      <c r="F98" t="n">
+        <v>3</v>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>2026-08-10 15:03:50</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/resultados/terraroxa/inventario_externos.xlsx
+++ b/resultados/terraroxa/inventario_externos.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
